--- a/data/pack/us/arroz.xlsx
+++ b/data/pack/us/arroz.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K561"/>
+  <dimension ref="A1:K562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -30601,7 +30601,7 @@
         </is>
       </c>
       <c r="E549" t="n">
-        <v>14.1</v>
+        <v>13.9</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -30711,7 +30711,7 @@
         </is>
       </c>
       <c r="E551" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -30766,7 +30766,7 @@
         </is>
       </c>
       <c r="E552" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -30821,7 +30821,7 @@
         </is>
       </c>
       <c r="E553" t="n">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -30876,7 +30876,7 @@
         </is>
       </c>
       <c r="E554" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -30931,7 +30931,7 @@
         </is>
       </c>
       <c r="E555" t="n">
-        <v>12.3</v>
+        <v>11.9</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         </is>
       </c>
       <c r="E556" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -31041,7 +31041,7 @@
         </is>
       </c>
       <c r="E557" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -31096,7 +31096,7 @@
         </is>
       </c>
       <c r="E558" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="E559" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -31206,7 +31206,7 @@
         </is>
       </c>
       <c r="E560" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -31289,6 +31289,61 @@
         </is>
       </c>
       <c r="K561" t="inlineStr">
+        <is>
+          <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>arroz</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>cwt</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>USDA National Agricultural Statistics Service (Quick Stats)</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>US-PD</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
         <is>
           <t>Source: USDA National Agricultural Statistics Service (NASS), Quick Stats</t>
         </is>
@@ -31388,7 +31443,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
     </row>
@@ -31399,7 +31454,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="9">
@@ -31494,7 +31549,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
